--- a/Dia 11-Crear un Buscador/Sumar+BuscarX.xlsx
+++ b/Dia 11-Crear un Buscador/Sumar+BuscarX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Win10\Downloads\00 - FEDE\Udemy\Excel\ACTUALIZACION 2020\Sección Búsquedas\Lección 8 - Sumar Funciones BuscarX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\Dia 11-Crear un Buscador\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF377FB8-2A98-4639-A785-304D29251762}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D60EFA-F8C1-41A8-ACFD-08702D22E751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{501AE460-DB50-4E86-98FA-B4BC8379AB9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{501AE460-DB50-4E86-98FA-B4BC8379AB9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -91,10 +94,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,6 +122,21 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -164,20 +182,25 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -494,132 +517,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42480279-275C-4C7A-9011-0668AE8DF9EF}">
   <dimension ref="B2:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="2" max="6" width="15.77734375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="6">
         <v>36568</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="6">
         <v>43812</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="6">
         <v>38705</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="1" t="s">
+      <c r="F5" s="8">
+        <f>SUM(_xlfn.XLOOKUP(F2,B3:B14,C3:C14):_xlfn.XLOOKUP(F3,B3:B14,C3:C14))</f>
+        <v>308224</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="6">
         <v>16598</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="1" t="s">
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="6">
         <v>49487</v>
       </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
+      <c r="F7" s="9"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="6">
         <v>42805</v>
       </c>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="1" t="s">
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="6">
         <v>43124</v>
       </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="6">
         <v>37125</v>
       </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="1" t="s">
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="6">
         <v>43674</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="1" t="s">
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="6">
         <v>18486</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="1" t="s">
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="6">
         <v>48338</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="1" t="s">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="6">
         <v>26950</v>
       </c>
     </row>
